--- a/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. The software architecture based on microservices is a design and software development approach where an application is built as a collection of small and independent services that communicate with each other.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. [...] The system must be scalable to handle an increase in the number of users and volume of data. [...] To adapt to future growth and ensure performance.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29, C_07</t>
+          <t>C_07, Scalability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33, 41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle an increase in the number of users and volume of data.; Ability to increase server resources and maintain performance with a 50% increase in workload.; 12g. Expansion or Growth Requirements</t>
+          <t>12g. Expansion or Growth Requirements; Scalability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,266 +506,66 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6383</v>
+        <v>0.6826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where a subject maintains a list of observers. [...] When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>C_06, Adaptability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The user interface must be intuitive and easy to use for non-technical users.; 11a. Ease of Use Requirements</t>
+          <t>14c. Adaptability Requirements; Adaptability</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>System Service; Next.js</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7467</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>In the case of this application, said services run on Amazon EC2 instances and are managed by Docker, which manages the execution of the containers.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C_04</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>12e. Robustness or Fault Tolerance Requirements</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.648</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Component-Based</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD09</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14c. Adaptability Requirements</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD07</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5961</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Singleton Pattern</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>It is designed to simplify access and database management</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.639</v>
+        <v>0.6024</v>
       </c>
     </row>
   </sheetData>
